--- a/Bill_of_Material.xlsx
+++ b/Bill_of_Material.xlsx
@@ -5,18 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dirk/Libelle/OpenVario/e-Vario/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dirk/Documents/GitHub/FreeVarioGauge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1A93D2-9129-AC4D-A7E5-C8A8C943E9C7}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE31D72D-7771-0142-A12F-F1F424447885}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{A71850B3-3A10-CA42-999C-A02A84AA5A96}"/>
   </bookViews>
   <sheets>
     <sheet name="Vario" sheetId="1" r:id="rId1"/>
-    <sheet name="BOM-PCB1" sheetId="2" r:id="rId2"/>
-    <sheet name="BOM-PCB2" sheetId="3" r:id="rId3"/>
-    <sheet name="BOM-PCB3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="135">
   <si>
     <t>Value</t>
   </si>
@@ -108,9 +105,6 @@
     <t>Vario Board 2</t>
   </si>
   <si>
-    <t>SMD-Widerstand, 0805, 10 kOhm</t>
-  </si>
-  <si>
     <t>SMD-0805 10,0K</t>
   </si>
   <si>
@@ -207,9 +201,6 @@
     <t>X7R-G0805 1,0/50</t>
   </si>
   <si>
-    <t>C9, C11, C14</t>
-  </si>
-  <si>
     <t>C6, C7, C10, C12, C13</t>
   </si>
   <si>
@@ -222,120 +213,10 @@
     <t>NCP 1117 ST50T3G</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
-    <t>Designator</t>
-  </si>
-  <si>
-    <t>Footprint</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>LCSC Part #</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>optional</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
-    <t>SO-16</t>
-  </si>
-  <si>
-    <t>C143432</t>
-  </si>
-  <si>
     <t>EA WF050-40ST</t>
   </si>
   <si>
-    <t>MOLEX 541044031</t>
-  </si>
-  <si>
-    <t>C164172</t>
-  </si>
-  <si>
-    <t>ZIF SMD</t>
-  </si>
-  <si>
-    <t>10nF</t>
-  </si>
-  <si>
-    <t>C83170</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>0805</t>
-  </si>
-  <si>
-    <t>C49678</t>
-  </si>
-  <si>
-    <t>1µF</t>
-  </si>
-  <si>
-    <t>10µF</t>
-  </si>
-  <si>
-    <t>C77083</t>
-  </si>
-  <si>
-    <t>C77075</t>
-  </si>
-  <si>
     <t>PAM8302A</t>
-  </si>
-  <si>
-    <t>C113367</t>
-  </si>
-  <si>
-    <t>MSOP8</t>
-  </si>
-  <si>
-    <t>PAM8302AASCR</t>
-  </si>
-  <si>
-    <t>C26537</t>
-  </si>
-  <si>
-    <t>SOT-223</t>
-  </si>
-  <si>
-    <t>C17314</t>
-  </si>
-  <si>
-    <t>C84376</t>
   </si>
   <si>
     <t>https://www.luna-electronic.de/de/tft-displays/newhaven-display-nhd-2-4-240320cf-csxn-f-2-4-sunlight-readable-tft.html</t>
@@ -562,12 +443,18 @@
   <si>
     <t>PEC11R-4230F-S0012</t>
   </si>
+  <si>
+    <t>SMD chip resistor, 0805, 100 Ohm</t>
+  </si>
+  <si>
+    <t>RND 0805 1 100</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -603,25 +490,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri Light (Überschriften)"/>
@@ -647,21 +515,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -669,42 +531,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1375,7 +1215,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1394,7 +1234,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1408,7 +1248,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -1425,10 +1265,10 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1437,7 +1277,7 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1451,14 +1291,14 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B10" t="s">
@@ -1476,7 +1316,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -1488,15 +1328,15 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
@@ -1505,16 +1345,16 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C13" s="3">
         <v>1</v>
@@ -1523,16 +1363,16 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -1541,16 +1381,16 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="C15" s="3">
         <v>1</v>
@@ -1559,16 +1399,16 @@
         <v>10</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -1577,16 +1417,16 @@
         <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="C17" s="3">
         <v>1</v>
@@ -1595,13 +1435,13 @@
         <v>10</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s">
         <v>20</v>
@@ -1618,10 +1458,10 @@
     </row>
     <row r="19" spans="1:6" s="3" customFormat="1">
       <c r="A19" s="3" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C19" s="3">
         <v>5</v>
@@ -1630,15 +1470,15 @@
         <v>10</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="3" customFormat="1">
       <c r="A20" s="3" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="C20" s="3">
         <v>4</v>
@@ -1647,15 +1487,15 @@
         <v>10</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -1669,10 +1509,10 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="C22" s="3">
         <v>2</v>
@@ -1681,15 +1521,15 @@
         <v>10</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="C23" s="3">
         <v>1</v>
@@ -1698,15 +1538,15 @@
         <v>10</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -1715,15 +1555,15 @@
         <v>10</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="C25" s="3">
         <v>2</v>
@@ -1732,12 +1572,12 @@
         <v>10</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="4" customFormat="1">
       <c r="A26" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>23</v>
@@ -1751,10 +1591,10 @@
     </row>
     <row r="27" spans="1:6" s="4" customFormat="1">
       <c r="A27" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27" s="3">
         <v>1</v>
@@ -1763,16 +1603,16 @@
         <v>10</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F27" s="3"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1781,15 +1621,15 @@
         <v>10</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -1798,21 +1638,21 @@
         <v>10</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="3" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E30" s="3"/>
     </row>
@@ -1842,10 +1682,10 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -1854,15 +1694,15 @@
         <v>10</v>
       </c>
       <c r="E35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -1871,16 +1711,16 @@
         <v>10</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F36" s="3"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="3" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1889,15 +1729,15 @@
         <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1906,42 +1746,42 @@
       <c r="E38" s="3"/>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" s="9">
+      <c r="A39" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="6">
         <v>1</v>
       </c>
       <c r="D39" s="2"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="9"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="6"/>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="B40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" t="s">
         <v>49</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1">
       <c r="A41" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -1950,12 +1790,12 @@
         <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -1972,27 +1812,27 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="B43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" t="s">
         <v>30</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="B44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -2001,15 +1841,15 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="B45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -2018,15 +1858,15 @@
         <v>10</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2035,15 +1875,15 @@
         <v>10</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="3" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="B47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -2052,7 +1892,7 @@
         <v>10</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2065,30 +1905,30 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D50" s="2"/>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="B51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" t="s">
         <v>33</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="B52" t="s">
         <v>15</v>
@@ -2100,12 +1940,12 @@
         <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>19</v>
@@ -2117,12 +1957,12 @@
         <v>10</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="B54" t="s">
         <v>19</v>
@@ -2134,12 +1974,12 @@
         <v>10</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="B55" t="s">
         <v>19</v>
@@ -2151,12 +1991,12 @@
         <v>10</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -2165,26 +2005,26 @@
         <v>10</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="B57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -2193,30 +2033,30 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="C59">
         <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="C60">
         <v>2</v>
       </c>
       <c r="D60" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2277,426 +2117,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AE57722-5B75-1D40-B9DC-B066A479B666}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="B12" s="3"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="C13" s="8"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="C14" s="8"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="C15" s="8"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://lcsc.com/product-detail/RS232-ICs_Maxim-Integrated_MAX3232ECWE_Maxim-Integrated-MAX3232ECWE_C143432.html" xr:uid="{FFB8C294-ADB0-F040-8E94-CA7FA2EA3011}"/>
-    <hyperlink ref="D3" r:id="rId2" display="https://lcsc.com/product-detail/FFC-FPC-Connectors_MOLEX_541044031_MOLEX-541044031_C164172.html" xr:uid="{A7338377-6668-2044-8707-7702B89446DA}"/>
-    <hyperlink ref="D5" r:id="rId3" display="https://lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_10nF-103-10-50V_C83170.html" xr:uid="{898EF980-0C37-1645-A0A7-204CDB314404}"/>
-    <hyperlink ref="D7" r:id="rId4" display="https://lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_muRata_GRM21BR71H105KA12L_1uF-105-10-50V_C77083.html" xr:uid="{1D7CFD7E-0378-D34D-93C2-E2A1F7CCE8B6}"/>
-    <hyperlink ref="D9" r:id="rId5" display="https://lcsc.com/product-detail/Audio-Power-OpAmps_Diodes-Incorporated_PAM8302AASCR_Diodes-Incorporated-PAM8302AASCR_C113367.html" xr:uid="{E725EF93-6260-8C48-A42F-BB8CA19F9EFB}"/>
-    <hyperlink ref="A9" r:id="rId6" display="https://lcsc.com/product-detail/Audio-Power-OpAmps_Diodes-Incorporated_PAM8302AASCR_Diodes-Incorporated-PAM8302AASCR_C113367.html" xr:uid="{D6D8886E-D7E2-A846-BA93-6765604167F3}"/>
-    <hyperlink ref="D10" r:id="rId7" display="https://lcsc.com/product-detail/Low-Dropout-Regulators-LDO_ON-Semiconductor-ON-NCP1117ST50T3G_C17314.html" xr:uid="{1C2BF8A9-1D03-DD4D-87A2-7145C42F989B}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B9D977-3A0D-9F42-A6D8-BF8241070D0D}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="34.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="B5" s="3"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="B6" s="3"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="B7" s="3"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="B8" s="3"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="B9" s="3"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="B12" s="3"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="B13" s="3"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="C14" s="8"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5151FA7D-8764-CA4A-9E1E-220B2BFCB1B2}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="34.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="B5" s="3"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="B6" s="3"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="B7" s="3"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="B8" s="3"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="B9" s="3"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="B12" s="3"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="B13" s="3"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="C14" s="8"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Bill_of_Material.xlsx
+++ b/Bill_of_Material.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dirk/Documents/GitHub/FreeVarioGauge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE31D72D-7771-0142-A12F-F1F424447885}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535A31F0-7290-974E-A6C8-2B59A27C12C9}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{A71850B3-3A10-CA42-999C-A02A84AA5A96}"/>
   </bookViews>
@@ -124,9 +124,6 @@
   </si>
   <si>
     <t>R1</t>
-  </si>
-  <si>
-    <t>PIH T16SHM4N253B</t>
   </si>
   <si>
     <t>RND 205-00654</t>
@@ -387,9 +384,6 @@
     <t>JST - crimp contact, socket - XH</t>
   </si>
   <si>
-    <t>Potentiometer, 25 kOhm</t>
-  </si>
-  <si>
     <t>Pinheader female, 10-pin</t>
   </si>
   <si>
@@ -448,6 +442,12 @@
   </si>
   <si>
     <t>RND 0805 1 100</t>
+  </si>
+  <si>
+    <t>Potentiometer, 25 kOhm or 22 kOhm</t>
+  </si>
+  <si>
+    <t>PIH T16SHM4N253B or PO4M-LOG 22K</t>
   </si>
 </sst>
 </file>
@@ -866,8 +866,8 @@
     <col min="1" max="1" width="53.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="95.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.5" customWidth="1"/>
+    <col min="5" max="5" width="31.1640625" bestFit="1" customWidth="1"/>
     <col min="257" max="257" width="53.5" bestFit="1" customWidth="1"/>
     <col min="258" max="258" width="14.5" bestFit="1" customWidth="1"/>
     <col min="259" max="259" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -1215,7 +1215,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1234,7 +1234,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1248,7 +1248,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1277,7 +1277,7 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" t="s">
         <v>69</v>
-      </c>
-      <c r="E9" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1316,7 +1316,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -1328,15 +1328,15 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
@@ -1345,16 +1345,16 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C13" s="3">
         <v>1</v>
@@ -1363,16 +1363,16 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -1381,16 +1381,16 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C15" s="3">
         <v>1</v>
@@ -1399,16 +1399,16 @@
         <v>10</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -1417,16 +1417,16 @@
         <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C17" s="3">
         <v>1</v>
@@ -1435,13 +1435,13 @@
         <v>10</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s">
         <v>20</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="19" spans="1:6" s="3" customFormat="1">
       <c r="A19" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3">
         <v>5</v>
@@ -1470,15 +1470,15 @@
         <v>10</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="3" customFormat="1">
       <c r="A20" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20" s="3">
         <v>4</v>
@@ -1487,15 +1487,15 @@
         <v>10</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C22" s="3">
         <v>2</v>
@@ -1521,15 +1521,15 @@
         <v>10</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C23" s="3">
         <v>1</v>
@@ -1538,15 +1538,15 @@
         <v>10</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -1555,15 +1555,15 @@
         <v>10</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C25" s="3">
         <v>2</v>
@@ -1572,12 +1572,12 @@
         <v>10</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="4" customFormat="1">
       <c r="A26" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>23</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="27" spans="1:6" s="4" customFormat="1">
       <c r="A27" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C27" s="3">
         <v>1</v>
@@ -1603,16 +1603,16 @@
         <v>10</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F27" s="3"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1621,15 +1621,15 @@
         <v>10</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -1638,21 +1638,21 @@
         <v>10</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E30" s="3"/>
     </row>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -1711,16 +1711,16 @@
         <v>10</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F36" s="3"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B38" t="s">
         <v>28</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C39" s="6">
         <v>1</v>
@@ -1761,41 +1761,41 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" t="s">
         <v>48</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B41" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" t="s">
         <v>67</v>
-      </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B43" t="s">
         <v>29</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B44" t="s">
         <v>29</v>
@@ -1841,15 +1841,15 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -1858,15 +1858,15 @@
         <v>10</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -1875,15 +1875,15 @@
         <v>10</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -1892,7 +1892,7 @@
         <v>10</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1911,7 +1911,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="B51" t="s">
         <v>32</v>
@@ -1923,12 +1923,12 @@
         <v>10</v>
       </c>
       <c r="E51" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B52" t="s">
         <v>15</v>
@@ -1940,12 +1940,12 @@
         <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>19</v>
@@ -1957,12 +1957,12 @@
         <v>10</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B54" t="s">
         <v>19</v>
@@ -1974,12 +1974,12 @@
         <v>10</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B55" t="s">
         <v>19</v>
@@ -1991,12 +1991,12 @@
         <v>10</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -2005,26 +2005,26 @@
         <v>10</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -2033,30 +2033,30 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C59">
         <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C60">
         <v>2</v>
       </c>
       <c r="D60" t="s">
+        <v>36</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:5">

--- a/Bill_of_Material.xlsx
+++ b/Bill_of_Material.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dirk/Documents/GitHub/FreeVarioGauge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535A31F0-7290-974E-A6C8-2B59A27C12C9}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B40C8C5-E496-474F-B4BF-15F6085CE0AB}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{A71850B3-3A10-CA42-999C-A02A84AA5A96}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="137">
   <si>
     <t>Value</t>
   </si>
@@ -448,6 +448,12 @@
   </si>
   <si>
     <t>PIH T16SHM4N253B or PO4M-LOG 22K</t>
+  </si>
+  <si>
+    <t>PJ-242 - audio jack 2,5mm</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
   </si>
 </sst>
 </file>
@@ -860,7 +866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE93BCC-B60F-D148-9D08-040AD6C1FD16}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="53.5" bestFit="1" customWidth="1"/>
@@ -1896,42 +1902,40 @@
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="3" t="s">
+      <c r="A48" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>136</v>
+      </c>
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3"/>
-    </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="3"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D50" s="2"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B51" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" t="s">
-        <v>134</v>
-      </c>
+      <c r="D51" s="2"/>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -1940,114 +1944,117 @@
         <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C53" s="3">
-        <v>1</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>41</v>
+        <v>113</v>
+      </c>
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B54" t="s">
+        <v>116</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C54" s="3">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B55" t="s">
         <v>19</v>
       </c>
       <c r="C55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
+      </c>
+      <c r="B56" t="s">
+        <v>19</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B57" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
+      <c r="D57" t="s">
+        <v>10</v>
+      </c>
       <c r="E57" s="3" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
+      </c>
+      <c r="B58" t="s">
+        <v>35</v>
       </c>
       <c r="C58">
-        <v>2</v>
-      </c>
-      <c r="E58" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C59">
         <v>2</v>
       </c>
-      <c r="D59" t="s">
-        <v>36</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>123</v>
-      </c>
+      <c r="E59" s="3"/>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -2056,24 +2063,34 @@
         <v>36</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61" t="s">
+        <v>36</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61" s="2"/>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="4"/>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2"/>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="4"/>
-      <c r="E64" s="4"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="4"/>
@@ -2093,10 +2110,11 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="4"/>
-      <c r="D69" s="2"/>
+      <c r="E69" s="4"/>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="4"/>
+      <c r="D70" s="2"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="4"/>
@@ -2106,13 +2124,16 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="4"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D5" r:id="rId1" xr:uid="{7F86150E-47FD-DA4A-9270-93DC9349E90E}"/>
     <hyperlink ref="D34" r:id="rId2" xr:uid="{291D8364-1659-9C40-8C0D-A90D0A1EBE5D}"/>
-    <hyperlink ref="E59" r:id="rId3" display="https://www.okw.com/de/Kombikn%C3%B6pfe/A2510030.htm?var=af9c94b0-c2e5-11e2-8e2c-0050568225d7" xr:uid="{793912D7-3AE5-B64B-B387-83FB71750F27}"/>
-    <hyperlink ref="E60" r:id="rId4" display="https://www.okw.com/de/Kombikn%C3%B6pfe-Zubeh%C3%B6r/A4110000.htm" xr:uid="{6CBEB647-38E6-FE49-9E02-7C7E2E54AE89}"/>
+    <hyperlink ref="E60" r:id="rId3" display="https://www.okw.com/de/Kombikn%C3%B6pfe/A2510030.htm?var=af9c94b0-c2e5-11e2-8e2c-0050568225d7" xr:uid="{793912D7-3AE5-B64B-B387-83FB71750F27}"/>
+    <hyperlink ref="E61" r:id="rId4" display="https://www.okw.com/de/Kombikn%C3%B6pfe-Zubeh%C3%B6r/A4110000.htm" xr:uid="{6CBEB647-38E6-FE49-9E02-7C7E2E54AE89}"/>
     <hyperlink ref="D30" r:id="rId5" xr:uid="{CD6A2158-00CE-3142-9BE4-E087F48664CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Bill_of_Material.xlsx
+++ b/Bill_of_Material.xlsx
@@ -5,15 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dirk/Documents/GitHub/FreeVarioGauge/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dirk/Libelle/OpenVario/e-Vario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B40C8C5-E496-474F-B4BF-15F6085CE0AB}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FBA9F5-E750-3F49-8A08-2DE269E6D56B}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{A71850B3-3A10-CA42-999C-A02A84AA5A96}"/>
   </bookViews>
   <sheets>
     <sheet name="Vario" sheetId="1" r:id="rId1"/>
+    <sheet name="BOM-PCB1" sheetId="2" r:id="rId2"/>
+    <sheet name="BOM-PCB2" sheetId="3" r:id="rId3"/>
+    <sheet name="BOM-PCB3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="164">
   <si>
     <t>Value</t>
   </si>
@@ -105,6 +108,9 @@
     <t>Vario Board 2</t>
   </si>
   <si>
+    <t>SMD-Widerstand, 0805, 10 kOhm</t>
+  </si>
+  <si>
     <t>SMD-0805 10,0K</t>
   </si>
   <si>
@@ -159,9 +165,6 @@
     <t>NCP 1117 ST33T3G </t>
   </si>
   <si>
-    <t>JST XH2P ST90</t>
-  </si>
-  <si>
     <t>JST XH2P BU</t>
   </si>
   <si>
@@ -198,6 +201,9 @@
     <t>X7R-G0805 1,0/50</t>
   </si>
   <si>
+    <t>C9, C11, C14</t>
+  </si>
+  <si>
     <t>C6, C7, C10, C12, C13</t>
   </si>
   <si>
@@ -210,10 +216,120 @@
     <t>NCP 1117 ST50T3G</t>
   </si>
   <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Designator</t>
+  </si>
+  <si>
+    <t>Footprint</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>LCSC Part #</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>optional</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>SO-16</t>
+  </si>
+  <si>
+    <t>C143432</t>
+  </si>
+  <si>
     <t>EA WF050-40ST</t>
   </si>
   <si>
+    <t>MOLEX 541044031</t>
+  </si>
+  <si>
+    <t>C164172</t>
+  </si>
+  <si>
+    <t>ZIF SMD</t>
+  </si>
+  <si>
+    <t>10nF</t>
+  </si>
+  <si>
+    <t>C83170</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>0805</t>
+  </si>
+  <si>
+    <t>C49678</t>
+  </si>
+  <si>
+    <t>1µF</t>
+  </si>
+  <si>
+    <t>10µF</t>
+  </si>
+  <si>
+    <t>C77083</t>
+  </si>
+  <si>
+    <t>C77075</t>
+  </si>
+  <si>
     <t>PAM8302A</t>
+  </si>
+  <si>
+    <t>C113367</t>
+  </si>
+  <si>
+    <t>MSOP8</t>
+  </si>
+  <si>
+    <t>PAM8302AASCR</t>
+  </si>
+  <si>
+    <t>C26537</t>
+  </si>
+  <si>
+    <t>SOT-223</t>
+  </si>
+  <si>
+    <t>C17314</t>
+  </si>
+  <si>
+    <t>C84376</t>
   </si>
   <si>
     <t>https://www.luna-electronic.de/de/tft-displays/newhaven-display-nhd-2-4-240320cf-csxn-f-2-4-sunlight-readable-tft.html</t>
@@ -396,9 +512,6 @@
     <t>JST - socket housing, 1x3-pin - XH</t>
   </si>
   <si>
-    <t>JST — pin header, 90°, 1x2-pin - XH</t>
-  </si>
-  <si>
     <t>JST — socket housing, 1x2-pin - XH</t>
   </si>
   <si>
@@ -444,23 +557,29 @@
     <t>RND 0805 1 100</t>
   </si>
   <si>
-    <t>Potentiometer, 25 kOhm or 22 kOhm</t>
-  </si>
-  <si>
-    <t>PIH T16SHM4N253B or PO4M-LOG 22K</t>
+    <t>PIH T16SHM4N253B oder PO4M-LOG 22K</t>
+  </si>
+  <si>
+    <t>Potentiometer, 25 kOhm bzw. 22kOhm</t>
   </si>
   <si>
     <t>PJ-242 - audio jack 2,5mm</t>
   </si>
   <si>
     <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>JST XH3P ST90</t>
+  </si>
+  <si>
+    <t>JST - Stiftleiste, 90°, 1x3-polig - XH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -496,6 +615,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri Light (Überschriften)"/>
@@ -521,15 +659,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -537,20 +681,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -872,8 +1038,8 @@
     <col min="1" max="1" width="53.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.5" customWidth="1"/>
-    <col min="5" max="5" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="95.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.1640625" bestFit="1" customWidth="1"/>
     <col min="257" max="257" width="53.5" bestFit="1" customWidth="1"/>
     <col min="258" max="258" width="14.5" bestFit="1" customWidth="1"/>
     <col min="259" max="259" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -1221,7 +1387,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1240,7 +1406,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1254,7 +1420,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -1271,10 +1437,10 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1283,7 +1449,7 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1297,14 +1463,14 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B10" t="s">
@@ -1322,7 +1488,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -1334,15 +1500,15 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
@@ -1351,16 +1517,16 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3">
         <v>1</v>
@@ -1369,16 +1535,16 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -1387,16 +1553,16 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C15" s="3">
         <v>1</v>
@@ -1405,16 +1571,16 @@
         <v>10</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -1423,16 +1589,16 @@
         <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C17" s="3">
         <v>1</v>
@@ -1441,13 +1607,13 @@
         <v>10</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="B18" t="s">
         <v>20</v>
@@ -1464,7 +1630,7 @@
     </row>
     <row r="19" spans="1:6" s="3" customFormat="1">
       <c r="A19" s="3" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>54</v>
@@ -1481,10 +1647,10 @@
     </row>
     <row r="20" spans="1:6" s="3" customFormat="1">
       <c r="A20" s="3" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C20" s="3">
         <v>4</v>
@@ -1498,10 +1664,10 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -1515,10 +1681,10 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C22" s="3">
         <v>2</v>
@@ -1527,15 +1693,15 @@
         <v>10</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="C23" s="3">
         <v>1</v>
@@ -1544,15 +1710,15 @@
         <v>10</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -1561,15 +1727,15 @@
         <v>10</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="C25" s="3">
         <v>2</v>
@@ -1578,12 +1744,12 @@
         <v>10</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="4" customFormat="1">
       <c r="A26" s="3" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>23</v>
@@ -1597,7 +1763,7 @@
     </row>
     <row r="27" spans="1:6" s="4" customFormat="1">
       <c r="A27" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>51</v>
@@ -1609,33 +1775,33 @@
         <v>10</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F27" s="3"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="B28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -1649,10 +1815,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="3" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1688,7 +1854,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="B35" t="s">
         <v>49</v>
@@ -1700,12 +1866,12 @@
         <v>10</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>55</v>
@@ -1723,10 +1889,10 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1735,15 +1901,15 @@
         <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1752,22 +1918,22 @@
       <c r="E38" s="3"/>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" s="6">
+      <c r="A39" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="9">
         <v>1</v>
       </c>
       <c r="D39" s="2"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="6"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="9"/>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="B40" t="s">
         <v>47</v>
@@ -1784,10 +1950,10 @@
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1">
       <c r="A41" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B41" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -1796,12 +1962,12 @@
         <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -1818,10 +1984,10 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -1830,15 +1996,15 @@
         <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -1847,12 +2013,12 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="B45" t="s">
         <v>46</v>
@@ -1868,8 +2034,8 @@
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="3" t="s">
-        <v>117</v>
+      <c r="A46" t="s">
+        <v>163</v>
       </c>
       <c r="B46" t="s">
         <v>46</v>
@@ -1881,12 +2047,12 @@
         <v>10</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>44</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="3" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="B47" t="s">
         <v>46</v>
@@ -1898,12 +2064,12 @@
         <v>10</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" t="s">
-        <v>135</v>
+      <c r="A48" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="B48" t="s">
         <v>15</v>
@@ -1912,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="E48" s="3"/>
     </row>
@@ -1926,16 +2092,16 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D51" s="2"/>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -1944,12 +2110,12 @@
         <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="B53" t="s">
         <v>15</v>
@@ -1961,12 +2127,12 @@
         <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>19</v>
@@ -1978,12 +2144,12 @@
         <v>10</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="B55" t="s">
         <v>19</v>
@@ -1995,12 +2161,12 @@
         <v>10</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="B56" t="s">
         <v>19</v>
@@ -2012,12 +2178,12 @@
         <v>10</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -2026,26 +2192,26 @@
         <v>10</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="B58" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -2054,30 +2220,30 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="C60">
         <v>2</v>
       </c>
       <c r="D60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C61">
         <v>2</v>
       </c>
       <c r="D61" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2138,4 +2304,426 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AE57722-5B75-1D40-B9DC-B066A479B666}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" s="3"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="C13" s="8"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="C14" s="8"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="C15" s="8"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" display="https://lcsc.com/product-detail/RS232-ICs_Maxim-Integrated_MAX3232ECWE_Maxim-Integrated-MAX3232ECWE_C143432.html" xr:uid="{FFB8C294-ADB0-F040-8E94-CA7FA2EA3011}"/>
+    <hyperlink ref="D3" r:id="rId2" display="https://lcsc.com/product-detail/FFC-FPC-Connectors_MOLEX_541044031_MOLEX-541044031_C164172.html" xr:uid="{A7338377-6668-2044-8707-7702B89446DA}"/>
+    <hyperlink ref="D5" r:id="rId3" display="https://lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_10nF-103-10-50V_C83170.html" xr:uid="{898EF980-0C37-1645-A0A7-204CDB314404}"/>
+    <hyperlink ref="D7" r:id="rId4" display="https://lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_muRata_GRM21BR71H105KA12L_1uF-105-10-50V_C77083.html" xr:uid="{1D7CFD7E-0378-D34D-93C2-E2A1F7CCE8B6}"/>
+    <hyperlink ref="D9" r:id="rId5" display="https://lcsc.com/product-detail/Audio-Power-OpAmps_Diodes-Incorporated_PAM8302AASCR_Diodes-Incorporated-PAM8302AASCR_C113367.html" xr:uid="{E725EF93-6260-8C48-A42F-BB8CA19F9EFB}"/>
+    <hyperlink ref="A9" r:id="rId6" display="https://lcsc.com/product-detail/Audio-Power-OpAmps_Diodes-Incorporated_PAM8302AASCR_Diodes-Incorporated-PAM8302AASCR_C113367.html" xr:uid="{D6D8886E-D7E2-A846-BA93-6765604167F3}"/>
+    <hyperlink ref="D10" r:id="rId7" display="https://lcsc.com/product-detail/Low-Dropout-Regulators-LDO_ON-Semiconductor-ON-NCP1117ST50T3G_C17314.html" xr:uid="{1C2BF8A9-1D03-DD4D-87A2-7145C42F989B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B9D977-3A0D-9F42-A6D8-BF8241070D0D}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5" s="3"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6" s="3"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7" s="3"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8" s="3"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" s="3"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" s="3"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="B13" s="3"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="C14" s="8"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5151FA7D-8764-CA4A-9E1E-220B2BFCB1B2}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5" s="3"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6" s="3"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7" s="3"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8" s="3"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" s="3"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" s="3"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="B13" s="3"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="C14" s="8"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bill_of_Material.xlsx
+++ b/Bill_of_Material.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dirk/Libelle/OpenVario/e-Vario/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dirk/Libelle/OpenVario/e-Vario/Instructions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FBA9F5-E750-3F49-8A08-2DE269E6D56B}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9E11AE-5B96-6347-935F-DF51BA844D54}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{A71850B3-3A10-CA42-999C-A02A84AA5A96}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="162">
   <si>
     <t>Value</t>
   </si>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>NCP 1117 ST33T3G </t>
-  </si>
-  <si>
-    <t>JST XH2P BU</t>
   </si>
   <si>
     <t>﻿STF-WOELBKLAPPEN</t>
@@ -510,9 +507,6 @@
   </si>
   <si>
     <t>JST - socket housing, 1x3-pin - XH</t>
-  </si>
-  <si>
-    <t>JST — socket housing, 1x2-pin - XH</t>
   </si>
   <si>
     <t>Toggle switch 6A-125VAC, 1x On-Off-ON</t>
@@ -1387,7 +1381,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1406,7 +1400,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1420,7 +1414,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -1437,10 +1431,10 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1449,7 +1443,7 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1463,10 +1457,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" t="s">
         <v>94</v>
-      </c>
-      <c r="E9" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1488,7 +1482,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -1500,15 +1494,15 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
@@ -1517,16 +1511,16 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3">
         <v>1</v>
@@ -1535,16 +1529,16 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -1553,16 +1547,16 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C15" s="3">
         <v>1</v>
@@ -1571,16 +1565,16 @@
         <v>10</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -1589,16 +1583,16 @@
         <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17" s="3">
         <v>1</v>
@@ -1607,13 +1601,13 @@
         <v>10</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B18" t="s">
         <v>20</v>
@@ -1630,10 +1624,10 @@
     </row>
     <row r="19" spans="1:6" s="3" customFormat="1">
       <c r="A19" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" s="3">
         <v>5</v>
@@ -1642,15 +1636,15 @@
         <v>10</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="3" customFormat="1">
       <c r="A20" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C20" s="3">
         <v>4</v>
@@ -1659,15 +1653,15 @@
         <v>10</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -1681,10 +1675,10 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C22" s="3">
         <v>2</v>
@@ -1693,15 +1687,15 @@
         <v>10</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C23" s="3">
         <v>1</v>
@@ -1710,15 +1704,15 @@
         <v>10</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -1727,15 +1721,15 @@
         <v>10</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C25" s="3">
         <v>2</v>
@@ -1744,12 +1738,12 @@
         <v>10</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="4" customFormat="1">
       <c r="A26" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>23</v>
@@ -1763,10 +1757,10 @@
     </row>
     <row r="27" spans="1:6" s="4" customFormat="1">
       <c r="A27" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C27" s="3">
         <v>1</v>
@@ -1775,7 +1769,7 @@
         <v>10</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F27" s="3"/>
     </row>
@@ -1784,7 +1778,7 @@
         <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1798,7 +1792,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B29" t="s">
         <v>39</v>
@@ -1810,12 +1804,12 @@
         <v>10</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B30" t="s">
         <v>39</v>
@@ -1824,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E30" s="3"/>
     </row>
@@ -1854,10 +1848,10 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -1871,10 +1865,10 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -1883,16 +1877,16 @@
         <v>10</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F36" s="3"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1906,7 +1900,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B38" t="s">
         <v>29</v>
@@ -1919,10 +1913,10 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C39" s="9">
         <v>1</v>
@@ -1933,41 +1927,41 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" t="s">
         <v>47</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" t="s">
         <v>92</v>
-      </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
@@ -1984,7 +1978,7 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B43" t="s">
         <v>30</v>
@@ -2001,7 +1995,7 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B44" t="s">
         <v>30</v>
@@ -2013,15 +2007,15 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" t="s">
-        <v>143</v>
+      <c r="A45" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -2030,15 +2024,15 @@
         <v>10</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2047,15 +2041,15 @@
         <v>10</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -2069,7 +2063,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B48" t="s">
         <v>15</v>
@@ -2078,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E48" s="3"/>
     </row>
@@ -2098,7 +2092,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B52" t="s">
         <v>33</v>
@@ -2110,12 +2104,12 @@
         <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B53" t="s">
         <v>15</v>
@@ -2132,7 +2126,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>19</v>
@@ -2149,7 +2143,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B55" t="s">
         <v>19</v>
@@ -2166,7 +2160,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B56" t="s">
         <v>19</v>
@@ -2183,7 +2177,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -2197,7 +2191,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B58" t="s">
         <v>36</v>
@@ -2206,12 +2200,12 @@
         <v>1</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -2220,7 +2214,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -2229,12 +2223,12 @@
         <v>37</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -2318,16 +2312,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2338,24 +2332,24 @@
         <v>17</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2363,97 +2357,97 @@
         <v>26</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>86</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2461,13 +2455,13 @@
         <v>44</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2510,16 +2504,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2527,27 +2521,27 @@
         <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2625,16 +2619,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2642,27 +2636,27 @@
         <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:4">

--- a/Bill_of_Material.xlsx
+++ b/Bill_of_Material.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dirk/Libelle/OpenVario/e-Vario/Instructions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dirk/Documents/GitHub/FreeVarioGauge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9E11AE-5B96-6347-935F-DF51BA844D54}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF24A8A-117B-4448-BC0D-9F35705ED747}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{A71850B3-3A10-CA42-999C-A02A84AA5A96}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="163">
   <si>
     <t>Value</t>
   </si>
@@ -567,6 +567,9 @@
   </si>
   <si>
     <t>JST - Stiftleiste, 90°, 1x3-polig - XH</t>
+  </si>
+  <si>
+    <t>R1, R2, R3, R4, R5</t>
   </si>
 </sst>
 </file>
@@ -1851,10 +1854,10 @@
         <v>117</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>

--- a/Bill_of_Material.xlsx
+++ b/Bill_of_Material.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dirk/Documents/GitHub/FreeVarioGauge/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dirk/Libelle/OpenVario/e-Vario/Instructions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF24A8A-117B-4448-BC0D-9F35705ED747}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F0D5C5-AAA3-0148-8E44-15ADD7E67E41}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{A71850B3-3A10-CA42-999C-A02A84AA5A96}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="166">
   <si>
     <t>Value</t>
   </si>
@@ -570,6 +570,15 @@
   </si>
   <si>
     <t>R1, R2, R3, R4, R5</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>TS 4148-1206</t>
+  </si>
+  <si>
+    <t>TS 4148-1206 Switching diode, 75 V, 150 mA, G1206</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE93BCC-B60F-D148-9D08-040AD6C1FD16}">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="53.5" bestFit="1" customWidth="1"/>
@@ -1868,137 +1877,137 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="3">
+        <v>165</v>
+      </c>
+      <c r="B36" t="s">
+        <v>163</v>
+      </c>
+      <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>164</v>
+      </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="3">
+        <v>1</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="3"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>90</v>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
-      <c r="A38" t="s">
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
         <v>132</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>29</v>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38" s="2"/>
-      <c r="E38" s="3"/>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="9" t="s">
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B40" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C39" s="9">
-        <v>1</v>
-      </c>
-      <c r="D39" s="2"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="9"/>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" t="s">
+      <c r="C40" s="9">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="9"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
         <v>134</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>46</v>
       </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="15" customHeight="1">
-      <c r="A41" t="s">
+    <row r="42" spans="1:6" ht="15" customHeight="1">
+      <c r="A42" t="s">
         <v>135</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>91</v>
       </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" t="s">
-        <v>115</v>
-      </c>
-      <c r="B42" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42">
-        <v>2</v>
-      </c>
-      <c r="D42" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B44" t="s">
         <v>30</v>
@@ -2010,29 +2019,29 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>151</v>
+      </c>
+      <c r="B45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="3" t="s">
+    <row r="46" spans="1:6">
+      <c r="A46" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="B45" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" t="s">
-        <v>161</v>
       </c>
       <c r="B46" t="s">
         <v>45</v>
@@ -2044,78 +2053,78 @@
         <v>10</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="3" t="s">
-        <v>137</v>
+      <c r="A47" t="s">
+        <v>161</v>
       </c>
       <c r="B47" t="s">
         <v>45</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>40</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="3" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="s">
-        <v>159</v>
-      </c>
-      <c r="E48" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49" t="s">
+        <v>159</v>
+      </c>
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3"/>
-    </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="3"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D51" s="2"/>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B52" t="s">
-        <v>33</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" t="s">
-        <v>156</v>
-      </c>
+      <c r="D52" s="2"/>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -2124,114 +2133,117 @@
         <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C54" s="3">
-        <v>1</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>42</v>
+        <v>138</v>
+      </c>
+      <c r="B54" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B55" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C55" s="3">
+        <v>1</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B56" t="s">
         <v>19</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
+      </c>
+      <c r="B57" t="s">
+        <v>19</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B58" t="s">
-        <v>36</v>
+        <v>142</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
+      <c r="D58" t="s">
+        <v>10</v>
+      </c>
       <c r="E58" s="3" t="s">
-        <v>153</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
+      </c>
+      <c r="B59" t="s">
+        <v>36</v>
       </c>
       <c r="C59">
-        <v>2</v>
-      </c>
-      <c r="E59" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C60">
         <v>2</v>
       </c>
-      <c r="D60" t="s">
-        <v>37</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>146</v>
-      </c>
+      <c r="E60" s="3"/>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -2240,24 +2252,34 @@
         <v>37</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62" t="s">
+        <v>37</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62" s="2"/>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="4"/>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="4"/>
-      <c r="E65" s="4"/>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="4"/>
@@ -2277,10 +2299,11 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="4"/>
-      <c r="D70" s="2"/>
+      <c r="E70" s="4"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="4"/>
+      <c r="D71" s="2"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="4"/>
@@ -2290,13 +2313,16 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="4"/>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D5" r:id="rId1" xr:uid="{7F86150E-47FD-DA4A-9270-93DC9349E90E}"/>
     <hyperlink ref="D34" r:id="rId2" xr:uid="{291D8364-1659-9C40-8C0D-A90D0A1EBE5D}"/>
-    <hyperlink ref="E60" r:id="rId3" display="https://www.okw.com/de/Kombikn%C3%B6pfe/A2510030.htm?var=af9c94b0-c2e5-11e2-8e2c-0050568225d7" xr:uid="{793912D7-3AE5-B64B-B387-83FB71750F27}"/>
-    <hyperlink ref="E61" r:id="rId4" display="https://www.okw.com/de/Kombikn%C3%B6pfe-Zubeh%C3%B6r/A4110000.htm" xr:uid="{6CBEB647-38E6-FE49-9E02-7C7E2E54AE89}"/>
+    <hyperlink ref="E61" r:id="rId3" display="https://www.okw.com/de/Kombikn%C3%B6pfe/A2510030.htm?var=af9c94b0-c2e5-11e2-8e2c-0050568225d7" xr:uid="{793912D7-3AE5-B64B-B387-83FB71750F27}"/>
+    <hyperlink ref="E62" r:id="rId4" display="https://www.okw.com/de/Kombikn%C3%B6pfe-Zubeh%C3%B6r/A4110000.htm" xr:uid="{6CBEB647-38E6-FE49-9E02-7C7E2E54AE89}"/>
     <hyperlink ref="D30" r:id="rId5" xr:uid="{CD6A2158-00CE-3142-9BE4-E087F48664CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
